--- a/data/trans_dic/P70D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,95</t>
+          <t>1,5; 6,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,39</t>
+          <t>2,57; 6,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,53</t>
+          <t>2,52; 5,7</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,32</t>
+          <t>1,52; 5,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,34</t>
+          <t>1,39; 5,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,99</t>
+          <t>1,86; 5,08</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,56</t>
+          <t>0,13; 3,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 13,24</t>
+          <t>3,62; 13,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,58</t>
+          <t>0,55; 4,34</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,41</t>
+          <t>5,08; 9,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,37</t>
+          <t>3,9; 8,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,1</t>
+          <t>5,16; 8,17</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,8</t>
+          <t>2,57; 7,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 13,43</t>
+          <t>4,4; 13,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,25; 9,96</t>
+          <t>4,32; 10,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,57; 5,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,53; 7,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,52; 5,54</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>2,58; 5,14</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4,4; 7,21</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3,6; 5,56</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10)</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5527; 20939</t>
+          <t>5294; 21747</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7678; 20227</t>
+          <t>8143; 20107</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16568; 36989</t>
+          <t>16871; 38091</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4589; 19244</t>
+          <t>4631; 17978</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3948; 13457</t>
+          <t>3495; 13639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10627; 27786</t>
+          <t>10331; 28261</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>466; 17414</t>
+          <t>611; 17884</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2481; 9695</t>
+          <t>2648; 9919</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2168; 25741</t>
+          <t>3089; 24389</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28091; 52683</t>
+          <t>28446; 52914</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17990; 35663</t>
+          <t>16617; 34678</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51243; 79867</t>
+          <t>50827; 80549</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5278; 18587</t>
+          <t>6110; 18359</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16022; 50103</t>
+          <t>16427; 50962</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25988; 60895</t>
+          <t>26425; 61927</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76904</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81728</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>158631</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50004; 97862</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>65287; 103828</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>119093; 187551</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>76904</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>81728</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>158631</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>50024; 99937</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>63397; 103846</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>121832; 188269</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P70D_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P70D_R-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,18</t>
+          <t>1,45; 5,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,36</t>
+          <t>2,65; 6,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,7</t>
+          <t>2,43; 5,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,91</t>
+          <t>1,47; 6,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,41</t>
+          <t>1,58; 5,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,08</t>
+          <t>1,95; 4,91</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,66</t>
+          <t>0,96; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 13,55</t>
+          <t>3,36; 12,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,34</t>
+          <t>2,02; 5,62</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,46</t>
+          <t>4,51; 8,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,14</t>
+          <t>3,87; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,17</t>
+          <t>4,71; 7,66</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,71</t>
+          <t>2,48; 7,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 13,67</t>
+          <t>7,64; 13,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,13</t>
+          <t>5,58; 9,81</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,04</t>
+          <t>3,53; 5,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,21</t>
+          <t>4,86; 7,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,54</t>
+          <t>4,31; 5,82</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>26250</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5294; 21747</t>
+          <t>5535; 22241</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8143; 20107</t>
+          <t>8956; 22375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16871; 38091</t>
+          <t>17498; 37667</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>18537</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4631; 17978</t>
+          <t>4715; 19480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3495; 13639</t>
+          <t>4306; 15117</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10331; 28261</t>
+          <t>11598; 29181</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12315</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>611; 17884</t>
+          <t>2612; 12799</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2648; 9919</t>
+          <t>2789; 10005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3089; 24389</t>
+          <t>7169; 19893</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>40391</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25248</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63971</t>
+          <t>67183</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28446; 52914</t>
+          <t>28005; 54716</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16617; 34678</t>
+          <t>18516; 37069</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50827; 80549</t>
+          <t>51758; 84143</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>46393</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6110; 18359</t>
+          <t>7601; 22734</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16427; 50962</t>
+          <t>23912; 43656</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26425; 61927</t>
+          <t>34583; 60787</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>81728</t>
+          <t>87638</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158631</t>
+          <t>170677</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>50004; 97862</t>
+          <t>67261; 104593</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>65287; 103828</t>
+          <t>72124; 106154</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119093; 187551</t>
+          <t>145878; 197282</t>
         </is>
       </c>
     </row>
